--- a/workbooks/unit-b-data.xlsx
+++ b/workbooks/unit-b-data.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,7 +53,7 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00777777"/>
+      <color rgb="00555555"/>
       <sz val="9"/>
     </font>
     <font>
@@ -63,13 +63,31 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E8C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
+      <color rgb="001F4E8C"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Courier New"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00777777"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -86,8 +104,18 @@
         <fgColor rgb="001F2937"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEEFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F8FF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -95,11 +123,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="004F9DFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="004F9DFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="004F9DFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="004F9DFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="004F9DFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="004F9DFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="004F9DFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="004F9DFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="004F9DFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="004F9DFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="004F9DFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="004F9DFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="004F9DFF"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="004F9DFF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,8 +194,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -353,6 +454,41 @@
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Excel for Finance course</author>
+  </authors>
+  <commentList>
+    <comment ref="E6" authorId="0" shapeId="0">
+      <text>
+        <t>Type =VLOOKUP(E5,A6:B8,2,FALSE) here.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Excel for Finance course</author>
+  </authors>
+  <commentList>
+    <comment ref="B11" authorId="0" shapeId="0">
+      <text>
+        <t>Type =SUMIF(A6:A9,"Equity",B6:B9) here.</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>Type =COUNTIF(A6:A9,"Equity") here.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -683,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -707,28 +843,56 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>How to use this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Each tab has a blue 'YOUR TASK' box with numbered steps — read it first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yellow cells also have a small red comment triangle in the corner — hover over one for a quick reminder of exactly what to type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Compare your work against the 'Answer Key' tab at the end — it recalculates live, so it updates as you fill things in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Color legend:</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Yellow fill</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B10">
         <f> a cell you should fill in</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Blue text</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B11">
         <f> a hardcoded input/assumption</f>
         <v/>
       </c>
@@ -744,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -770,7 +934,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Yellow cells are for you to fill in. Everything else is provided.</t>
+          <t>🟡 Yellow cell = type something here.   🔵 Blue text = a given input.   Black text = a formula already provided.</t>
         </is>
       </c>
     </row>
@@ -837,19 +1001,55 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Task: in E6, use VLOOKUP to find the price for the ticker in E5, using an exact match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>✏️  YOUR TASK</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>1. In cell E6, use VLOOKUP to find the price of the ticker typed in E5.</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>2. Your lookup table is A6:B8. The price is in the 2nd column of that table.</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>3. Use an exact match (type FALSE, or 0, as the 4th argument) — otherwise VLOOKUP may silently return the wrong row.</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:F11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -859,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -883,7 +1083,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Yellow cells are for you to fill in. Everything else is provided.</t>
+          <t>🟡 Yellow cell = type something here.   🔵 Blue text = a given input.   Black text = a formula already provided.</t>
         </is>
       </c>
     </row>
@@ -961,19 +1161,46 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Task: B11 = SUMIF the Value column where Asset Class = "Equity". B12 = COUNTIF the Asset Class column for "Equity".</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>✏️  YOUR TASK</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>1. In B11, use SUMIF to total the Value column (B6:B9) only where the Asset Class column (A6:A9) says "Equity".</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>2. In B12, use COUNTIF to count how many rows in A6:A9 say "Equity".</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F15"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -983,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1008,7 +1235,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Yellow cells are for you to fill in. Everything else is provided.</t>
+          <t>🟡 Yellow cell = type something here.   🔵 Blue text = a given input.   Black text = a formula already provided.</t>
         </is>
       </c>
     </row>
@@ -1125,17 +1352,61 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Task: select A5:C11, press Ctrl+T to make it a Table, then use the dropdown on the Amount header to sort largest to smallest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>✏️  YOUR TASK</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>1. Click any cell inside A5:C11, then press Ctrl+T (or Insert &gt; Table). Confirm 'My table has headers' is checked.</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>2. Click the dropdown arrow on the Amount column header, and choose 'Sort Largest to Smallest'.</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>3. Open the 'B3 Tables (Example)' tab (next sheet over) to compare your result.</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>💡 No formula here — this task is about using the Table and Sort features in Excel's ribbon.</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F15"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1287,7 +1558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1314,7 +1585,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Yellow cells are for you to fill in. Everything else is provided.</t>
+          <t>🟡 Yellow cell = type something here.   🔵 Blue text = a given input.   Black text = a formula already provided.</t>
         </is>
       </c>
     </row>
@@ -1408,17 +1679,61 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Task: select B6:E8, apply a 3-color scale (Home &gt; Conditional Formatting &gt; Color Scales), then select A5:E8 and insert a Clustered Column chart (Insert &gt; Charts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>✏️  YOUR TASK</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>1. Select B6:E8 (just the numbers). Go to Home &gt; Conditional Formatting &gt; Color Scales, and pick a red-yellow-green scale.</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2. Select A5:E8 (headers + data). Go to Insert &gt; Charts &gt; Clustered Column.</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>3. Open the 'B4 Formatting-Charts (Ex)' tab to compare your result.</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>💡 No formula here — this task is about using the Conditional Formatting and Chart features in Excel's ribbon.</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:F12"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1605,7 +1920,7 @@
           <t>E6</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>ƒ =VLOOKUP(E5,A6:B8,2,FALSE)</t>
         </is>
@@ -1626,7 +1941,7 @@
           <t>B11 (Total Equity)</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ƒ =SUMIF(A6:A9,"Equity",B6:B9)</t>
         </is>
@@ -1647,7 +1962,7 @@
           <t>B12 (Count Equity)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>ƒ =COUNTIF(A6:A9,"Equity")</t>
         </is>
@@ -1658,7 +1973,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Note: 'Live check' pulls today's value from your own sheet, so once you fill in the yellow cells correctly it will match what you typed.</t>
         </is>
